--- a/data/trans_orig/P21B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P21B-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según tipo de servicio de urgencias utilizado en 2007</t>
+          <t>Población según a dónde pertenecía el último servicio de urgencias que utilizó en los últimos 12 meses en 2007 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>835</t>
+          <t>832</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7827</t>
+          <t>7085</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>3,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>6920</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,03%</t>
+          <t>2,35%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1744</t>
+          <t>1770</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>11034</t>
+          <t>10158</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,32%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>1,88%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>912</t>
+          <t>992</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8905</t>
+          <t>8780</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1017</t>
+          <t>1008</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>10321</t>
+          <t>9185</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -901,7 +901,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,02%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3710</t>
+          <t>3846</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15825</t>
+          <t>15241</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,71%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,83%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>995</t>
+          <t>997</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10610</t>
+          <t>10485</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -979,7 +979,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,36%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -999,7 +999,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>7870</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,22%</t>
+          <t>0,21%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,3%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2000</t>
+          <t>2389</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>14335</t>
+          <t>13687</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,37%</t>
+          <t>0,44%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,66%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37381</t>
+          <t>37870</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>62176</t>
+          <t>61607</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>18,9%</t>
+          <t>19,15%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,44%</t>
+          <t>31,15%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75907</t>
+          <t>76344</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>109640</t>
+          <t>109154</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,23%</t>
+          <t>22,36%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>32,11%</t>
+          <t>31,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>119666</t>
+          <t>121282</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>161541</t>
+          <t>162640</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,19%</t>
+          <t>22,49%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>29,96%</t>
+          <t>30,16%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>125379</t>
+          <t>125235</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>150731</t>
+          <t>150921</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,39%</t>
+          <t>63,32%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,21%</t>
+          <t>76,31%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>222241</t>
+          <t>222711</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>256835</t>
+          <t>257789</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,08%</t>
+          <t>65,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,22%</t>
+          <t>75,49%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>358385</t>
+          <t>358285</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>402440</t>
+          <t>400152</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,46%</t>
+          <t>66,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,63%</t>
+          <t>74,2%</t>
         </is>
       </c>
     </row>
@@ -1415,97 +1415,97 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>740</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>1976</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>4132</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,2%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="J10" s="2" t="inlineStr">
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>1,1%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K10" s="2" t="inlineStr">
+      <c r="R10" s="2" t="inlineStr">
         <is>
           <t>740</t>
         </is>
       </c>
-      <c r="L10" s="2" t="inlineStr">
+      <c r="S10" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>4453</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,2%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
+      <c r="T10" s="2" t="inlineStr">
+        <is>
+          <t>3598</t>
+        </is>
+      </c>
+      <c r="U10" s="2" t="inlineStr">
+        <is>
+          <t>0,11%</t>
+        </is>
+      </c>
+      <c r="V10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>1,18%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>740</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" s="2" t="inlineStr">
-        <is>
-          <t>4445</t>
-        </is>
-      </c>
-      <c r="U10" s="2" t="inlineStr">
-        <is>
-          <t>0,11%</t>
-        </is>
-      </c>
-      <c r="V10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,68%</t>
+          <t>0,55%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>875</t>
+          <t>877</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7179</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,77 +1548,77 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>2,74%</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>6573</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2769</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>14470</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>1,75%</t>
+        </is>
+      </c>
+      <c r="O11" s="2" t="inlineStr">
+        <is>
+          <t>0,74%</t>
+        </is>
+      </c>
+      <c r="P11" s="2" t="inlineStr">
+        <is>
+          <t>3,84%</t>
+        </is>
+      </c>
+      <c r="Q11" s="2" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="R11" s="2" t="inlineStr">
+        <is>
+          <t>9248</t>
+        </is>
+      </c>
+      <c r="S11" s="2" t="inlineStr">
+        <is>
+          <t>4089</t>
+        </is>
+      </c>
+      <c r="T11" s="2" t="inlineStr">
+        <is>
+          <t>16750</t>
+        </is>
+      </c>
+      <c r="U11" s="2" t="inlineStr">
+        <is>
+          <t>1,41%</t>
+        </is>
+      </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>0,62%</t>
+        </is>
+      </c>
+      <c r="W11" s="2" t="inlineStr">
+        <is>
           <t>2,55%</t>
-        </is>
-      </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>6573</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2862</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>14434</t>
-        </is>
-      </c>
-      <c r="N11" s="2" t="inlineStr">
-        <is>
-          <t>1,75%</t>
-        </is>
-      </c>
-      <c r="O11" s="2" t="inlineStr">
-        <is>
-          <t>0,76%</t>
-        </is>
-      </c>
-      <c r="P11" s="2" t="inlineStr">
-        <is>
-          <t>3,83%</t>
-        </is>
-      </c>
-      <c r="Q11" s="2" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="R11" s="2" t="inlineStr">
-        <is>
-          <t>9248</t>
-        </is>
-      </c>
-      <c r="S11" s="2" t="inlineStr">
-        <is>
-          <t>4549</t>
-        </is>
-      </c>
-      <c r="T11" s="2" t="inlineStr">
-        <is>
-          <t>17442</t>
-        </is>
-      </c>
-      <c r="U11" s="2" t="inlineStr">
-        <is>
-          <t>1,41%</t>
-        </is>
-      </c>
-      <c r="V11" s="2" t="inlineStr">
-        <is>
-          <t>0,69%</t>
-        </is>
-      </c>
-      <c r="W11" s="2" t="inlineStr">
-        <is>
-          <t>2,65%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1043</t>
+          <t>1044</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11865</t>
+          <t>11916</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,22%</t>
+          <t>4,24%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>996</t>
+          <t>990</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10118</t>
+          <t>10361</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1696,7 +1696,7 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,75%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>3724</t>
+          <t>4186</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16223</t>
+          <t>16182</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,46%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52851</t>
+          <t>52943</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>83101</t>
+          <t>82710</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,8%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,57%</t>
+          <t>29,43%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>96520</t>
+          <t>98013</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>132314</t>
+          <t>136535</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>25,64%</t>
+          <t>26,04%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>35,15%</t>
+          <t>36,27%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>159839</t>
+          <t>161419</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>206778</t>
+          <t>206183</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,31%</t>
+          <t>24,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,36%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>190136</t>
+          <t>189804</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>221325</t>
+          <t>221333</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,7 +1882,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,65%</t>
+          <t>67,53%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>232083</t>
+          <t>229207</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>270085</t>
+          <t>268135</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>61,65%</t>
+          <t>60,89%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,75%</t>
+          <t>71,23%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>432174</t>
+          <t>431216</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>480263</t>
+          <t>477897</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,73%</t>
+          <t>65,58%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>72,68%</t>
         </is>
       </c>
     </row>
@@ -2097,97 +2097,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2060</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,59%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1994</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2036</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>958</t>
+          <t>885</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>11347</t>
+          <t>9939</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>843</t>
+          <t>851</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>8013</t>
+          <t>7860</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2260,12 +2260,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,8%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,55%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2661</t>
+          <t>2707</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>13661</t>
+          <t>15019</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2295,12 +2295,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,46%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>7,36%</t>
+          <t>8,09%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1114</t>
+          <t>1097</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10792</t>
+          <t>10798</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,7 +2338,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>932</t>
+          <t>930</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>9560</t>
+          <t>10340</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2378,7 +2378,7 @@
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,01%</t>
+          <t>9,75%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3394</t>
+          <t>3450</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16581</t>
+          <t>16016</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,93%</t>
+          <t>8,62%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13591</t>
+          <t>14092</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30346</t>
+          <t>30581</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,07%</t>
+          <t>17,7%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,12%</t>
+          <t>38,41%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>14739</t>
+          <t>15226</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32156</t>
+          <t>32606</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,89%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,31%</t>
+          <t>30,73%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33194</t>
+          <t>33489</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>56383</t>
+          <t>57025</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>18,03%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,71%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40267</t>
+          <t>40511</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>58348</t>
+          <t>58023</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,58%</t>
+          <t>50,89%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>72,89%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>68275</t>
+          <t>66455</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>86521</t>
+          <t>85247</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>64,35%</t>
+          <t>62,64%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>113886</t>
+          <t>113881</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>139704</t>
+          <t>139559</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,33%</t>
+          <t>61,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,15%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>838</t>
+          <t>833</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7580</t>
+          <t>7237</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,36%</t>
+          <t>1,3%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2819,7 +2819,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8178</t>
+          <t>8723</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2530</t>
+          <t>2157</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12046</t>
+          <t>12112</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,18%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,87%</t>
+          <t>0,88%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5555</t>
+          <t>4823</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18434</t>
+          <t>18411</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2907,7 +2907,7 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7429</t>
+          <t>7911</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>23028</t>
+          <t>23840</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,9%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,79%</t>
+          <t>2,89%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>15570</t>
+          <t>14912</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>35854</t>
+          <t>34178</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,08%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,59%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6405</t>
+          <t>6685</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22318</t>
+          <t>21291</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,15%</t>
+          <t>1,2%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>4,0%</t>
+          <t>3,81%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>4236</t>
+          <t>5294</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>17489</t>
+          <t>18871</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,64%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,12%</t>
+          <t>2,29%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14068</t>
+          <t>14165</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>33892</t>
+          <t>34411</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3095,7 +3095,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,45%</t>
+          <t>2,49%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>117606</t>
+          <t>117442</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>159123</t>
+          <t>159373</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>21,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,49%</t>
+          <t>28,54%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>201395</t>
+          <t>205256</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>256348</t>
+          <t>256541</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,44%</t>
+          <t>24,91%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,11%</t>
+          <t>31,13%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>336815</t>
+          <t>335936</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>399940</t>
+          <t>400741</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,36%</t>
+          <t>24,3%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,93%</t>
+          <t>28,99%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>372502</t>
+          <t>372893</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>414546</t>
+          <t>416360</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,7%</t>
+          <t>66,77%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,23%</t>
+          <t>74,56%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>538971</t>
+          <t>539307</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>595206</t>
+          <t>590802</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,41%</t>
+          <t>65,45%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>72,23%</t>
+          <t>71,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>927786</t>
+          <t>931911</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>994856</t>
+          <t>998117</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,11%</t>
+          <t>67,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>71,96%</t>
+          <t>72,2%</t>
         </is>
       </c>
     </row>
@@ -3497,7 +3497,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según tipo de servicio de urgencias utilizado en 2012</t>
+          <t>Población según a dónde pertenecía el último servicio de urgencias que utilizó en los últimos 12 meses en 2012 (tasa de respuesta: 99,68%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5364</t>
+          <t>5472</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,15%</t>
+          <t>2,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3727,62 +3727,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>1086</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>2043</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>6005</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,16%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,5%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>1086</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>5673</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,16%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,91%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>924</t>
+          <t>931</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>7799</t>
+          <t>8064</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7205</t>
+          <t>7284</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,76%</t>
+          <t>1,78%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1922</t>
+          <t>1959</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10401</t>
+          <t>10940</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3890,12 +3890,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,58%</t>
+          <t>1,66%</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>7324</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,53%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>10549</t>
+          <t>11047</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,57%</t>
+          <t>2,7%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>969</t>
+          <t>963</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>12697</t>
+          <t>10719</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,92%</t>
+          <t>1,62%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68950</t>
+          <t>68145</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>99928</t>
+          <t>101101</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,46%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>108065</t>
+          <t>108061</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>144671</t>
+          <t>145762</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4086,7 +4086,7 @@
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>186709</t>
+          <t>185522</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>234386</t>
+          <t>235152</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,3%</t>
+          <t>28,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,65%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>145514</t>
+          <t>143172</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>175639</t>
+          <t>176398</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>58,23%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,28%</t>
+          <t>70,59%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>261344</t>
+          <t>258993</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>297695</t>
+          <t>297655</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,77%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,64%</t>
+          <t>72,63%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>416169</t>
+          <t>414680</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>466023</t>
+          <t>462753</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,08%</t>
+          <t>62,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,64%</t>
+          <t>70,15%</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>4651</t>
+          <t>5527</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,21%</t>
+          <t>1,44%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4409,47 +4409,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>916</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2062</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>916</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4623</t>
+          <t>4599</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4487,12 +4487,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>—</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>2023</t>
+          <t>—</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4502,12 +4502,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0,53%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2904</t>
+          <t>2824</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>15119</t>
+          <t>13941</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,63%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,35%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>1983</t>
+          <t>2861</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>14498</t>
+          <t>13708</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4572,12 +4572,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,34%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>1,64%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3058</t>
+          <t>3056</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>17272</t>
+          <t>16086</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,5%</t>
+          <t>4,19%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1941</t>
+          <t>1928</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>12480</t>
+          <t>11876</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4655,42 +4655,42 @@
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
+          <t>2,63%</t>
+        </is>
+      </c>
+      <c r="Q12" s="2" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="R12" s="2" t="inlineStr">
+        <is>
+          <t>13720</t>
+        </is>
+      </c>
+      <c r="S12" s="2" t="inlineStr">
+        <is>
+          <t>7632</t>
+        </is>
+      </c>
+      <c r="T12" s="2" t="inlineStr">
+        <is>
+          <t>23140</t>
+        </is>
+      </c>
+      <c r="U12" s="2" t="inlineStr">
+        <is>
+          <t>1,64%</t>
+        </is>
+      </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>0,91%</t>
+        </is>
+      </c>
+      <c r="W12" s="2" t="inlineStr">
+        <is>
           <t>2,77%</t>
-        </is>
-      </c>
-      <c r="Q12" s="2" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="R12" s="2" t="inlineStr">
-        <is>
-          <t>13720</t>
-        </is>
-      </c>
-      <c r="S12" s="2" t="inlineStr">
-        <is>
-          <t>7780</t>
-        </is>
-      </c>
-      <c r="T12" s="2" t="inlineStr">
-        <is>
-          <t>22561</t>
-        </is>
-      </c>
-      <c r="U12" s="2" t="inlineStr">
-        <is>
-          <t>1,64%</t>
-        </is>
-      </c>
-      <c r="V12" s="2" t="inlineStr">
-        <is>
-          <t>0,93%</t>
-        </is>
-      </c>
-      <c r="W12" s="2" t="inlineStr">
-        <is>
-          <t>2,7%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>110000</t>
+          <t>107867</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>147140</t>
+          <t>145856</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,68%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,37%</t>
+          <t>38,03%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>132920</t>
+          <t>134825</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>173815</t>
+          <t>177887</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,47%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>39,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>256819</t>
+          <t>256993</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>311247</t>
+          <t>312048</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,77%</t>
+          <t>30,79%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,29%</t>
+          <t>37,39%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>226541</t>
+          <t>229190</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>264388</t>
+          <t>266538</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>59,76%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,94%</t>
+          <t>69,5%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>264223</t>
+          <t>261696</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>307548</t>
+          <t>305040</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,58%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>68,18%</t>
+          <t>67,63%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>499451</t>
+          <t>503451</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>555687</t>
+          <t>557802</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>59,84%</t>
+          <t>60,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>66,84%</t>
         </is>
       </c>
     </row>
@@ -5056,97 +5056,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1985</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,86%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>2148</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>1,88%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>2098</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,14%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4871</t>
+          <t>4617</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>7,01%</t>
+          <t>6,65%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2919</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>16112</t>
+          <t>14807</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>14,1%</t>
+          <t>12,95%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>3108</t>
+          <t>2848</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>16317</t>
+          <t>15498</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,69%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,88%</t>
+          <t>8,43%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>919</t>
+          <t>923</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>9064</t>
+          <t>8002</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,33%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,05%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2065</t>
+          <t>2132</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12772</t>
+          <t>12812</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,86%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4088</t>
+          <t>4985</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16297</t>
+          <t>17492</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,87%</t>
+          <t>9,52%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>25272</t>
+          <t>24819</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42427</t>
+          <t>42384</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>61,08%</t>
+          <t>61,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16198</t>
+          <t>15588</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>34012</t>
+          <t>33405</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,64%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,75%</t>
+          <t>29,22%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45888</t>
+          <t>45531</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>72296</t>
+          <t>70806</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,97%</t>
+          <t>24,78%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>39,34%</t>
+          <t>38,53%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>22928</t>
+          <t>23588</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40118</t>
+          <t>40288</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,01%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>58,0%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>65521</t>
+          <t>66030</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>86752</t>
+          <t>86737</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,32%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,89%</t>
+          <t>75,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94397</t>
+          <t>94989</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>122052</t>
+          <t>123149</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,37%</t>
+          <t>51,69%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,41%</t>
+          <t>67,01%</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>6932</t>
+          <t>7012</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5773,62 +5773,62 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M22" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N22" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P22" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q22" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R22" s="2" t="inlineStr">
+        <is>
+          <t>2002</t>
+        </is>
+      </c>
+      <c r="S22" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M22" s="2" t="inlineStr">
-        <is>
-          <t>2069</t>
-        </is>
-      </c>
-      <c r="N22" s="2" t="inlineStr">
+      <c r="T22" s="2" t="inlineStr">
+        <is>
+          <t>6457</t>
+        </is>
+      </c>
+      <c r="U22" s="2" t="inlineStr">
+        <is>
+          <t>0,12%</t>
+        </is>
+      </c>
+      <c r="V22" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O22" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P22" s="2" t="inlineStr">
-        <is>
-          <t>0,21%</t>
-        </is>
-      </c>
-      <c r="Q22" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R22" s="2" t="inlineStr">
-        <is>
-          <t>2002</t>
-        </is>
-      </c>
-      <c r="S22" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" s="2" t="inlineStr">
-        <is>
-          <t>6910</t>
-        </is>
-      </c>
-      <c r="U22" s="2" t="inlineStr">
-        <is>
-          <t>0,12%</t>
-        </is>
-      </c>
-      <c r="V22" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,41%</t>
+          <t>0,38%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>944</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>9650</t>
+          <t>8809</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8682</t>
+          <t>8875</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>25860</t>
+          <t>26632</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,89%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,65%</t>
+          <t>2,73%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>12503</t>
+          <t>11792</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>31188</t>
+          <t>30407</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,75%</t>
+          <t>0,7%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,81%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6880</t>
+          <t>6509</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22501</t>
+          <t>22791</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,98%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,2%</t>
+          <t>3,24%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8151</t>
+          <t>8218</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24612</t>
+          <t>24475</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6019,7 +6019,7 @@
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,52%</t>
+          <t>2,51%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>17432</t>
+          <t>17430</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>39129</t>
+          <t>39562</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6054,7 +6054,7 @@
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,33%</t>
+          <t>2,36%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>221025</t>
+          <t>221041</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>273441</t>
+          <t>274310</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6097,7 +6097,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>39,03%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>274502</t>
+          <t>274300</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>334998</t>
+          <t>333812</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,15%</t>
+          <t>28,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,35%</t>
+          <t>34,23%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>510197</t>
+          <t>512585</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>590606</t>
+          <t>593907</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>30,55%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,2%</t>
+          <t>35,39%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>410767</t>
+          <t>411648</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>462051</t>
+          <t>464856</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,44%</t>
+          <t>58,57%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>66,14%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>610025</t>
+          <t>607108</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>672627</t>
+          <t>670468</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>62,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,97%</t>
+          <t>68,75%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1038029</t>
+          <t>1036950</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1119401</t>
+          <t>1119659</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>61,86%</t>
+          <t>61,79%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,71%</t>
+          <t>66,72%</t>
         </is>
       </c>
     </row>
@@ -6456,7 +6456,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según tipo de servicio de urgencias utilizado en 2016</t>
+          <t>Población según a dónde pertenecía el último servicio de urgencias que utilizó en los últimos 12 meses en 2016 (tasa de respuesta: 98,06%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5706</t>
+          <t>6081</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,43%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5279</t>
+          <t>5293</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>818</t>
+          <t>806</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8283</t>
+          <t>8604</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6736,12 +6736,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>0,23%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,39%</t>
         </is>
       </c>
     </row>
@@ -6764,97 +6764,97 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>2262</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr">
-        <is>
-          <t>1866</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr">
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>9905</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>1,01%</t>
+        </is>
+      </c>
+      <c r="O5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
+      <c r="P5" s="2" t="inlineStr">
+        <is>
+          <t>4,44%</t>
+        </is>
+      </c>
+      <c r="Q5" s="2" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="K5" s="2" t="inlineStr">
+      <c r="R5" s="2" t="inlineStr">
         <is>
           <t>2262</t>
         </is>
       </c>
-      <c r="L5" s="2" t="inlineStr">
+      <c r="S5" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M5" s="2" t="inlineStr">
-        <is>
-          <t>8776</t>
-        </is>
-      </c>
-      <c r="N5" s="2" t="inlineStr">
-        <is>
-          <t>1,01%</t>
-        </is>
-      </c>
-      <c r="O5" s="2" t="inlineStr">
+      <c r="T5" s="2" t="inlineStr">
+        <is>
+          <t>8457</t>
+        </is>
+      </c>
+      <c r="U5" s="2" t="inlineStr">
+        <is>
+          <t>0,63%</t>
+        </is>
+      </c>
+      <c r="V5" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P5" s="2" t="inlineStr">
-        <is>
-          <t>3,93%</t>
-        </is>
-      </c>
-      <c r="Q5" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R5" s="2" t="inlineStr">
-        <is>
-          <t>2262</t>
-        </is>
-      </c>
-      <c r="S5" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" s="2" t="inlineStr">
-        <is>
-          <t>7768</t>
-        </is>
-      </c>
-      <c r="U5" s="2" t="inlineStr">
-        <is>
-          <t>0,63%</t>
-        </is>
-      </c>
-      <c r="V5" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,16%</t>
+          <t>2,35%</t>
         </is>
       </c>
     </row>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>4162</t>
+          <t>5545</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>4,04%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6912,62 +6912,62 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P6" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>1020</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M6" s="2" t="inlineStr">
-        <is>
-          <t>2196</t>
-        </is>
-      </c>
-      <c r="N6" s="2" t="inlineStr">
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>5151</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>0,28%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O6" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P6" s="2" t="inlineStr">
-        <is>
-          <t>0,98%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>1020</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>6865</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>0,28%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,91%</t>
+          <t>1,43%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>28266</t>
+          <t>27790</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47007</t>
+          <t>47902</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,6%</t>
+          <t>20,25%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>42202</t>
+          <t>41900</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>68092</t>
+          <t>69436</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,91%</t>
+          <t>18,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,51%</t>
+          <t>31,12%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>75594</t>
+          <t>74731</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>109575</t>
+          <t>110202</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,98%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,41%</t>
+          <t>30,58%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>86842</t>
+          <t>86720</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>106824</t>
+          <t>107799</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,29%</t>
+          <t>63,2%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>78,57%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>149936</t>
+          <t>149991</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>176666</t>
+          <t>177663</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,19%</t>
+          <t>67,22%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>243925</t>
+          <t>242493</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>279174</t>
+          <t>278930</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,69%</t>
+          <t>67,29%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,47%</t>
+          <t>77,41%</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6691</t>
+          <t>6766</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,99%</t>
+          <t>2,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7368,47 +7368,47 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P10" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="R10" s="2" t="inlineStr">
+        <is>
+          <t>1904</t>
+        </is>
+      </c>
+      <c r="S10" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>2000</t>
-        </is>
-      </c>
-      <c r="N10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="O10" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P10" s="2" t="inlineStr">
-        <is>
-          <t>0,52%</t>
-        </is>
-      </c>
-      <c r="Q10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="R10" s="2" t="inlineStr">
-        <is>
-          <t>1904</t>
-        </is>
-      </c>
-      <c r="S10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6646</t>
+          <t>6660</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>2905</t>
+          <t>3341</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14386</t>
+          <t>14303</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,27%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>5119</t>
+          <t>4481</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19516</t>
+          <t>18910</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,32%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>4,88%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10423</t>
+          <t>10754</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28277</t>
+          <t>28160</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,49%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,9%</t>
+          <t>3,89%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>9020</t>
+          <t>8841</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27613</t>
+          <t>27166</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,2%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6289</t>
+          <t>6332</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20732</t>
+          <t>20524</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,63%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,35%</t>
+          <t>5,3%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>19548</t>
+          <t>18138</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41971</t>
+          <t>41686</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,5%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,8%</t>
+          <t>5,76%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>73074</t>
+          <t>72924</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107013</t>
+          <t>107564</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,66%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,79%</t>
+          <t>31,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>104024</t>
+          <t>104192</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>140189</t>
+          <t>140988</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,84%</t>
+          <t>26,88%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,17%</t>
+          <t>36,38%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>186585</t>
+          <t>186477</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>236941</t>
+          <t>233568</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,77%</t>
+          <t>25,75%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>32,25%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>203122</t>
+          <t>202512</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>240017</t>
+          <t>240240</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,34%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,31%</t>
+          <t>71,37%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>224950</t>
+          <t>223799</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>262380</t>
+          <t>261692</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,04%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,7%</t>
+          <t>67,52%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>438997</t>
+          <t>437057</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>490722</t>
+          <t>489626</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,62%</t>
+          <t>60,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,76%</t>
+          <t>67,61%</t>
         </is>
       </c>
     </row>
@@ -8015,97 +8015,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>946</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2143</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>5028</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>0,7%</t>
+        </is>
+      </c>
+      <c r="O16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>2,9%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>3,75%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>946</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>4745</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
-        <is>
-          <t>0,7%</t>
-        </is>
-      </c>
-      <c r="O16" s="2" t="inlineStr">
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>3867</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
+        <is>
+          <t>0,45%</t>
+        </is>
+      </c>
+      <c r="V16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>3,54%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>946</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>5447</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,45%</t>
-        </is>
-      </c>
-      <c r="V16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>1,86%</t>
         </is>
       </c>
     </row>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6272</t>
+          <t>6264</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,49%</t>
+          <t>8,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9150</t>
+          <t>9272</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>25600</t>
+          <t>26713</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,82%</t>
+          <t>6,91%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,07%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10476</t>
+          <t>10820</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>27260</t>
+          <t>28478</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,2%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,1%</t>
+          <t>13,68%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3894</t>
+          <t>3824</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>15686</t>
+          <t>16323</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,17%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>21,23%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6157</t>
+          <t>6726</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20214</t>
+          <t>20384</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>4,59%</t>
+          <t>5,01%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,06%</t>
+          <t>15,19%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>14076</t>
+          <t>13250</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>31799</t>
+          <t>31119</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,76%</t>
+          <t>6,37%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>14,95%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7065</t>
+          <t>7689</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21532</t>
+          <t>22227</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>10,41%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>29,14%</t>
+          <t>30,08%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18514</t>
+          <t>18494</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>36796</t>
+          <t>37715</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,78%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>27,41%</t>
+          <t>28,1%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29556</t>
+          <t>29729</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>53059</t>
+          <t>52917</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,2%</t>
+          <t>14,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,49%</t>
+          <t>25,43%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40970</t>
+          <t>41410</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>57662</t>
+          <t>57762</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>56,04%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,04%</t>
+          <t>78,17%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>66358</t>
+          <t>66655</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>90306</t>
+          <t>89504</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>49,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112021</t>
+          <t>112043</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>141859</t>
+          <t>142262</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,82%</t>
+          <t>53,84%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,36%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>939</t>
+          <t>944</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9190</t>
+          <t>9332</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8717,7 +8717,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>1,7%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8021</t>
+          <t>7659</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,03%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2478</t>
+          <t>1901</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12233</t>
+          <t>13043</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,95%</t>
+          <t>1,01%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4448</t>
+          <t>4655</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17559</t>
+          <t>17087</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,81%</t>
+          <t>0,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,21%</t>
+          <t>3,12%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>17522</t>
+          <t>19523</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>41281</t>
+          <t>42872</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,62%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,54%</t>
+          <t>5,76%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>26357</t>
+          <t>26538</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>53409</t>
+          <t>52568</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,04%</t>
+          <t>2,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,13%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16598</t>
+          <t>16918</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>38504</t>
+          <t>39693</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,03%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,03%</t>
+          <t>7,25%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>15466</t>
+          <t>16397</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>34897</t>
+          <t>37045</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,08%</t>
+          <t>2,2%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,68%</t>
+          <t>4,97%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>37125</t>
+          <t>37904</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>65105</t>
+          <t>67188</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,87%</t>
+          <t>2,93%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,04%</t>
+          <t>5,2%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>120191</t>
+          <t>117729</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>161674</t>
+          <t>160906</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,94%</t>
+          <t>21,5%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,52%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>180938</t>
+          <t>181734</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>229517</t>
+          <t>229860</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,81%</t>
+          <t>30,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>313180</t>
+          <t>310415</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>377044</t>
+          <t>378226</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,23%</t>
+          <t>24,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,17%</t>
+          <t>29,26%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>346966</t>
+          <t>348131</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>392588</t>
+          <t>393296</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,35%</t>
+          <t>63,56%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,68%</t>
+          <t>71,81%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>458125</t>
+          <t>456347</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>512813</t>
+          <t>510424</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,5%</t>
+          <t>61,26%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,84%</t>
+          <t>68,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>821709</t>
+          <t>817245</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>890481</t>
+          <t>892280</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,57%</t>
+          <t>63,22%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>68,89%</t>
+          <t>69,03%</t>
         </is>
       </c>
     </row>
@@ -9415,7 +9415,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según tipo de servicio de urgencias utilizado en 2023</t>
+          <t>Población según a dónde pertenecía el último servicio de urgencias que utilizó en los últimos 12 meses en 2023 (tasa de respuesta: 99,95%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9615,7 +9615,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4148</t>
+          <t>4457</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9630,7 +9630,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9645,62 +9645,62 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="O4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P4" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="R4" s="2" t="inlineStr">
+        <is>
+          <t>759</t>
+        </is>
+      </c>
+      <c r="S4" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>1018</t>
-        </is>
-      </c>
-      <c r="N4" s="2" t="inlineStr">
+      <c r="T4" s="2" t="inlineStr">
+        <is>
+          <t>3817</t>
+        </is>
+      </c>
+      <c r="U4" s="2" t="inlineStr">
+        <is>
+          <t>0,22%</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O4" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P4" s="2" t="inlineStr">
-        <is>
-          <t>0,46%</t>
-        </is>
-      </c>
-      <c r="Q4" s="2" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="R4" s="2" t="inlineStr">
-        <is>
-          <t>759</t>
-        </is>
-      </c>
-      <c r="S4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" s="2" t="inlineStr">
-        <is>
-          <t>3798</t>
-        </is>
-      </c>
-      <c r="U4" s="2" t="inlineStr">
-        <is>
-          <t>0,22%</t>
-        </is>
-      </c>
-      <c r="V4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,09%</t>
         </is>
       </c>
     </row>
@@ -9728,7 +9728,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>4202</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9743,7 +9743,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,18%</t>
+          <t>3,0%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9758,12 +9758,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1109</t>
+          <t>1133</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7496</t>
+          <t>7566</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9773,12 +9773,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>0,52%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,42%</t>
+          <t>3,46%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9793,12 +9793,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1628</t>
+          <t>1416</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8303</t>
+          <t>8118</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9808,12 +9808,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,31%</t>
         </is>
       </c>
     </row>
@@ -9836,12 +9836,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>612</t>
+          <t>632</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6006</t>
+          <t>5888</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9851,12 +9851,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,46%</t>
+          <t>0,48%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,54%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9871,12 +9871,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>308</t>
+          <t>304</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5551</t>
+          <t>5771</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9891,42 +9891,42 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
+          <t>2,64%</t>
+        </is>
+      </c>
+      <c r="Q6" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="R6" s="2" t="inlineStr">
+        <is>
+          <t>3981</t>
+        </is>
+      </c>
+      <c r="S6" s="2" t="inlineStr">
+        <is>
+          <t>1554</t>
+        </is>
+      </c>
+      <c r="T6" s="2" t="inlineStr">
+        <is>
+          <t>8922</t>
+        </is>
+      </c>
+      <c r="U6" s="2" t="inlineStr">
+        <is>
+          <t>1,13%</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>0,44%</t>
+        </is>
+      </c>
+      <c r="W6" s="2" t="inlineStr">
+        <is>
           <t>2,54%</t>
-        </is>
-      </c>
-      <c r="Q6" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="R6" s="2" t="inlineStr">
-        <is>
-          <t>3981</t>
-        </is>
-      </c>
-      <c r="S6" s="2" t="inlineStr">
-        <is>
-          <t>1540</t>
-        </is>
-      </c>
-      <c r="T6" s="2" t="inlineStr">
-        <is>
-          <t>8528</t>
-        </is>
-      </c>
-      <c r="U6" s="2" t="inlineStr">
-        <is>
-          <t>1,13%</t>
-        </is>
-      </c>
-      <c r="V6" s="2" t="inlineStr">
-        <is>
-          <t>0,44%</t>
-        </is>
-      </c>
-      <c r="W6" s="2" t="inlineStr">
-        <is>
-          <t>2,43%</t>
         </is>
       </c>
     </row>
@@ -9949,12 +9949,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18515</t>
+          <t>18736</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>40287</t>
+          <t>41418</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -9964,12 +9964,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,0%</t>
+          <t>14,17%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,47%</t>
+          <t>31,32%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9984,12 +9984,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>30307</t>
+          <t>31043</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>47818</t>
+          <t>48414</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -9999,12 +9999,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,84%</t>
+          <t>14,18%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>21,84%</t>
+          <t>22,11%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10019,12 +10019,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>54774</t>
+          <t>53422</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>83296</t>
+          <t>82481</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10034,12 +10034,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,6%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,72%</t>
+          <t>23,49%</t>
         </is>
       </c>
     </row>
@@ -10062,12 +10062,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87811</t>
+          <t>87211</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>110264</t>
+          <t>110070</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10077,12 +10077,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,4%</t>
+          <t>65,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,24%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10097,12 +10097,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>165160</t>
+          <t>164721</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>184226</t>
+          <t>182942</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10112,12 +10112,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,43%</t>
+          <t>75,23%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,13%</t>
+          <t>83,55%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10132,12 +10132,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>259694</t>
+          <t>260091</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>288748</t>
+          <t>290306</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10147,12 +10147,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,94%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,22%</t>
+          <t>82,66%</t>
         </is>
       </c>
     </row>
@@ -10292,12 +10292,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1038</t>
+          <t>1315</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9199</t>
+          <t>9680</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10307,12 +10307,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,33%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,28%</t>
+          <t>2,4%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10327,12 +10327,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>878</t>
+          <t>880</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9412</t>
+          <t>9176</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10347,7 +10347,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,4%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10362,12 +10362,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3130</t>
+          <t>3034</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14565</t>
+          <t>14556</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10377,12 +10377,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,37%</t>
         </is>
       </c>
     </row>
@@ -10405,12 +10405,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3197</t>
+          <t>3053</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14011</t>
+          <t>13639</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10420,12 +10420,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,47%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10440,12 +10440,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3757</t>
+          <t>3769</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>19992</t>
+          <t>20094</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10455,12 +10455,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,05%</t>
+          <t>3,07%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10475,12 +10475,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>9006</t>
+          <t>8310</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>29739</t>
+          <t>28354</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10490,12 +10490,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,81%</t>
+          <t>2,68%</t>
         </is>
       </c>
     </row>
@@ -10518,12 +10518,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>7378</t>
+          <t>8161</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>29229</t>
+          <t>30762</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1,83%</t>
+          <t>2,02%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,24%</t>
+          <t>7,62%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10553,12 +10553,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>10079</t>
+          <t>8042</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41310</t>
+          <t>41599</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10568,12 +10568,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,54%</t>
+          <t>1,23%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,31%</t>
+          <t>6,35%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10588,12 +10588,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>21130</t>
+          <t>18386</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>58954</t>
+          <t>57231</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10603,12 +10603,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,0%</t>
+          <t>1,74%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,57%</t>
+          <t>5,41%</t>
         </is>
       </c>
     </row>
@@ -10631,12 +10631,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63164</t>
+          <t>62601</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>100576</t>
+          <t>102127</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10646,12 +10646,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,64%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,9%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10666,12 +10666,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36525</t>
+          <t>36151</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>132306</t>
+          <t>133717</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10681,12 +10681,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,58%</t>
+          <t>5,52%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,2%</t>
+          <t>20,42%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10701,12 +10701,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>83376</t>
+          <t>82819</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>216102</t>
+          <t>218319</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10716,12 +10716,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,87%</t>
+          <t>7,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,41%</t>
+          <t>20,62%</t>
         </is>
       </c>
     </row>
@@ -10744,12 +10744,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>275109</t>
+          <t>275425</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>316656</t>
+          <t>317914</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10759,12 +10759,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,12%</t>
+          <t>68,2%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,41%</t>
+          <t>78,72%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10779,12 +10779,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>464311</t>
+          <t>463323</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>598417</t>
+          <t>603677</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10794,12 +10794,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,89%</t>
+          <t>70,74%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>91,37%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10814,12 +10814,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>758215</t>
+          <t>760995</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>937294</t>
+          <t>949477</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10829,12 +10829,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>71,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>88,52%</t>
+          <t>89,67%</t>
         </is>
       </c>
     </row>
@@ -10974,97 +10974,97 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
           <t>0</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>1896</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="I16" s="2" t="inlineStr">
-        <is>
-          <t>1,36%</t>
-        </is>
-      </c>
-      <c r="J16" s="2" t="inlineStr">
+      <c r="O16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="P16" s="2" t="inlineStr">
+        <is>
+          <t>—%</t>
+        </is>
+      </c>
+      <c r="Q16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="K16" s="2" t="inlineStr">
+      <c r="R16" s="2" t="inlineStr">
         <is>
           <t>0</t>
         </is>
       </c>
-      <c r="L16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="M16" s="2" t="inlineStr">
-        <is>
-          <t>1374</t>
-        </is>
-      </c>
-      <c r="N16" s="2" t="inlineStr">
+      <c r="S16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="T16" s="2" t="inlineStr">
+        <is>
+          <t>—</t>
+        </is>
+      </c>
+      <c r="U16" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="O16" s="2" t="inlineStr">
-        <is>
-          <t>0%</t>
-        </is>
-      </c>
-      <c r="P16" s="2" t="inlineStr">
-        <is>
-          <t>0,8%</t>
-        </is>
-      </c>
-      <c r="Q16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="R16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" s="2" t="inlineStr">
-        <is>
-          <t>1573</t>
-        </is>
-      </c>
-      <c r="U16" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>0%</t>
+          <t>—%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>0,51%</t>
+          <t>—%</t>
         </is>
       </c>
     </row>
@@ -11087,12 +11087,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>5724</t>
+          <t>6161</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21248</t>
+          <t>21201</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11102,12 +11102,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,11%</t>
+          <t>4,42%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11122,12 +11122,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9084</t>
+          <t>9677</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>22533</t>
+          <t>23805</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11137,12 +11137,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,31%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,16%</t>
+          <t>13,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11157,12 +11157,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>19563</t>
+          <t>17869</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>39640</t>
+          <t>37643</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11172,12 +11172,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>6,3%</t>
+          <t>5,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,76%</t>
+          <t>12,12%</t>
         </is>
       </c>
     </row>
@@ -11200,12 +11200,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9468</t>
+          <t>9935</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>25612</t>
+          <t>26781</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,12 +11215,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>6,79%</t>
+          <t>7,13%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>18,37%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -11235,12 +11235,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6397</t>
+          <t>6169</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>17745</t>
+          <t>18271</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11250,12 +11250,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,74%</t>
+          <t>3,6%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,67%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11270,12 +11270,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>19020</t>
+          <t>18595</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>39096</t>
+          <t>37673</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11285,12 +11285,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>5,99%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,59%</t>
+          <t>12,13%</t>
         </is>
       </c>
     </row>
@@ -11313,12 +11313,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13941</t>
+          <t>13309</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>35073</t>
+          <t>33868</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11328,12 +11328,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,0%</t>
+          <t>9,55%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>25,16%</t>
+          <t>24,29%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11348,12 +11348,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33114</t>
+          <t>33416</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>53519</t>
+          <t>56638</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11363,12 +11363,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,35%</t>
+          <t>19,52%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>31,27%</t>
+          <t>33,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11383,12 +11383,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>52645</t>
+          <t>51920</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>82947</t>
+          <t>83065</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11398,12 +11398,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,95%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,74%</t>
         </is>
       </c>
     </row>
@@ -11426,12 +11426,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>76311</t>
+          <t>74509</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>100803</t>
+          <t>101241</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11441,12 +11441,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>54,73%</t>
+          <t>53,44%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,3%</t>
+          <t>72,62%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11461,12 +11461,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>89510</t>
+          <t>89818</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>112970</t>
+          <t>114230</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11476,12 +11476,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,29%</t>
+          <t>52,47%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,0%</t>
+          <t>66,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11496,12 +11496,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>172125</t>
+          <t>173369</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>206482</t>
+          <t>209060</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11511,12 +11511,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,42%</t>
+          <t>55,82%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>66,48%</t>
+          <t>67,31%</t>
         </is>
       </c>
     </row>
@@ -11656,12 +11656,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1687</t>
+          <t>1756</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10269</t>
+          <t>10467</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11671,12 +11671,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,25%</t>
+          <t>0,26%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,52%</t>
+          <t>1,55%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11691,12 +11691,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>845</t>
+          <t>923</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8752</t>
+          <t>9035</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11706,12 +11706,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,08%</t>
+          <t>0,09%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11726,12 +11726,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>3279</t>
+          <t>4100</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15086</t>
+          <t>15785</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11741,12 +11741,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,19%</t>
+          <t>0,24%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,92%</t>
         </is>
       </c>
     </row>
@@ -11769,12 +11769,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12725</t>
+          <t>12485</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>31106</t>
+          <t>30091</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11784,12 +11784,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,85%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,6%</t>
+          <t>4,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11804,12 +11804,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>15451</t>
+          <t>13111</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42559</t>
+          <t>41370</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11819,12 +11819,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,48%</t>
+          <t>1,25%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>3,96%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11839,12 +11839,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>31149</t>
+          <t>31142</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>64576</t>
+          <t>63669</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11859,7 +11859,7 @@
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,7%</t>
         </is>
       </c>
     </row>
@@ -11882,12 +11882,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>22979</t>
+          <t>23477</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>49415</t>
+          <t>51729</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11897,12 +11897,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,4%</t>
+          <t>3,48%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,32%</t>
+          <t>7,66%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11917,12 +11917,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>18978</t>
+          <t>17523</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>52127</t>
+          <t>53696</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -11932,12 +11932,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,82%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,99%</t>
+          <t>5,14%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11952,12 +11952,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>47421</t>
+          <t>46367</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>94121</t>
+          <t>91606</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -11967,12 +11967,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,76%</t>
+          <t>2,69%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,47%</t>
+          <t>5,32%</t>
         </is>
       </c>
     </row>
@@ -11995,12 +11995,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>106899</t>
+          <t>106742</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>157174</t>
+          <t>153293</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12010,12 +12010,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,82%</t>
+          <t>15,8%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>23,27%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12030,12 +12030,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>93525</t>
+          <t>95308</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>218368</t>
+          <t>218536</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12045,12 +12045,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>8,95%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12065,12 +12065,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>195325</t>
+          <t>196163</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>350317</t>
+          <t>353698</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12080,12 +12080,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,35%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,36%</t>
+          <t>20,56%</t>
         </is>
       </c>
     </row>
@@ -12108,12 +12108,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>459288</t>
+          <t>459560</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>513625</t>
+          <t>513456</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12123,12 +12123,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,99%</t>
+          <t>68,03%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,03%</t>
+          <t>76,01%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12143,12 +12143,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>738390</t>
+          <t>737789</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>916466</t>
+          <t>914456</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12158,12 +12158,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,65%</t>
+          <t>70,6%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,69%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12178,12 +12178,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1222837</t>
+          <t>1224116</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1453689</t>
+          <t>1438063</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12193,12 +12193,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,07%</t>
+          <t>71,14%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>84,49%</t>
+          <t>83,58%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P21B-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P21B-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>832</t>
+          <t>830</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>7085</t>
+          <t>7258</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -753,7 +753,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,58%</t>
+          <t>3,67%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -773,7 +773,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>7224</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -788,7 +788,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,12%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>1770</t>
+          <t>1764</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>10158</t>
+          <t>10673</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -823,7 +823,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,88%</t>
+          <t>1,98%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>992</t>
+          <t>1017</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8780</t>
+          <t>9166</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1008</t>
+          <t>986</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9185</t>
+          <t>9004</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,3%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>2,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>3846</t>
+          <t>4014</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>15241</t>
+          <t>15211</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,71%</t>
+          <t>0,74%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>2,82%</t>
         </is>
       </c>
     </row>
@@ -959,12 +959,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>997</t>
+          <t>1001</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>10485</t>
+          <t>11170</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -974,12 +974,12 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,5%</t>
+          <t>0,51%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,65%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -994,12 +994,12 @@
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>737</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>7870</t>
+          <t>7385</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,21%</t>
+          <t>0,22%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,3%</t>
+          <t>2,16%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -1029,12 +1029,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>2389</t>
+          <t>2531</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>13687</t>
+          <t>14075</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -1044,12 +1044,12 @@
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,47%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,61%</t>
         </is>
       </c>
     </row>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>37870</t>
+          <t>37739</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>61607</t>
+          <t>61499</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1087,12 +1087,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,15%</t>
+          <t>19,08%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,15%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1107,12 +1107,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>76344</t>
+          <t>75931</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>109154</t>
+          <t>107227</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1122,12 +1122,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>22,36%</t>
+          <t>22,24%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,97%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1142,12 +1142,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>121282</t>
+          <t>122234</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>162640</t>
+          <t>162757</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1157,12 +1157,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,49%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,16%</t>
+          <t>30,18%</t>
         </is>
       </c>
     </row>
@@ -1185,12 +1185,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>125235</t>
+          <t>125348</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>150921</t>
+          <t>150601</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1200,12 +1200,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,32%</t>
+          <t>63,38%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>76,31%</t>
+          <t>76,14%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1220,12 +1220,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>222711</t>
+          <t>223323</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>257789</t>
+          <t>257293</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1235,12 +1235,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>65,22%</t>
+          <t>65,4%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>75,49%</t>
+          <t>75,35%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1255,12 +1255,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>358285</t>
+          <t>355498</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>400152</t>
+          <t>397514</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1270,12 +1270,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,44%</t>
+          <t>65,92%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,2%</t>
+          <t>73,72%</t>
         </is>
       </c>
     </row>
@@ -1455,7 +1455,7 @@
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>4132</t>
+          <t>3762</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1470,7 +1470,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,1%</t>
+          <t>1,0%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1490,7 +1490,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>3598</t>
+          <t>4877</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1505,7 +1505,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,55%</t>
+          <t>0,74%</t>
         </is>
       </c>
     </row>
@@ -1528,12 +1528,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>877</t>
+          <t>865</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>7705</t>
+          <t>7166</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1548,7 +1548,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>2,74%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1563,12 +1563,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2769</t>
+          <t>2766</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>14470</t>
+          <t>13685</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1578,12 +1578,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,74%</t>
+          <t>0,73%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,84%</t>
+          <t>3,64%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1598,12 +1598,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>4089</t>
+          <t>4740</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>16750</t>
+          <t>17388</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1613,12 +1613,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,62%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,55%</t>
+          <t>2,64%</t>
         </is>
       </c>
     </row>
@@ -1641,12 +1641,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1044</t>
+          <t>1050</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>11916</t>
+          <t>12276</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1661,7 +1661,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,24%</t>
+          <t>4,37%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -1676,12 +1676,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>990</t>
+          <t>949</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>10361</t>
+          <t>9245</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -1691,12 +1691,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,25%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,75%</t>
+          <t>2,46%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -1711,12 +1711,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>4186</t>
+          <t>3797</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>16182</t>
+          <t>16639</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -1726,12 +1726,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,46%</t>
+          <t>2,53%</t>
         </is>
       </c>
     </row>
@@ -1754,12 +1754,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>52943</t>
+          <t>52382</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>82710</t>
+          <t>80300</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1769,12 +1769,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,84%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>29,43%</t>
+          <t>28,57%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1789,12 +1789,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>98013</t>
+          <t>96715</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>136535</t>
+          <t>132149</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1804,12 +1804,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,04%</t>
+          <t>25,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,27%</t>
+          <t>35,1%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1824,12 +1824,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>161419</t>
+          <t>159930</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>206183</t>
+          <t>206412</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1839,12 +1839,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>24,55%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>31,36%</t>
+          <t>31,39%</t>
         </is>
       </c>
     </row>
@@ -1867,12 +1867,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>189804</t>
+          <t>192470</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>221333</t>
+          <t>223094</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1882,12 +1882,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>67,53%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,75%</t>
+          <t>79,38%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1902,12 +1902,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>229207</t>
+          <t>230706</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>268135</t>
+          <t>268973</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1917,12 +1917,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>60,89%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>71,45%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1937,12 +1937,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>431216</t>
+          <t>431761</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>477897</t>
+          <t>481192</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1952,12 +1952,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>65,58%</t>
+          <t>65,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>73,19%</t>
         </is>
       </c>
     </row>
@@ -2210,12 +2210,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>885</t>
+          <t>925</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>9939</t>
+          <t>9989</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2225,12 +2225,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>1,11%</t>
+          <t>1,16%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>12,55%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2245,12 +2245,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>851</t>
+          <t>844</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>7860</t>
+          <t>8017</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2265,7 +2265,7 @@
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>7,41%</t>
+          <t>7,56%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2280,12 +2280,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2707</t>
+          <t>2710</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15019</t>
+          <t>14604</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2300,7 +2300,7 @@
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,09%</t>
+          <t>7,86%</t>
         </is>
       </c>
     </row>
@@ -2323,12 +2323,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>1097</t>
+          <t>1003</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>10798</t>
+          <t>10233</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -2338,12 +2338,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,38%</t>
+          <t>1,26%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>12,85%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -2358,12 +2358,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>930</t>
+          <t>942</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>10340</t>
+          <t>10149</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -2373,12 +2373,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>9,75%</t>
+          <t>9,57%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -2393,12 +2393,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>3450</t>
+          <t>3368</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>16016</t>
+          <t>15873</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -2408,12 +2408,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,81%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>8,62%</t>
+          <t>8,55%</t>
         </is>
       </c>
     </row>
@@ -2436,12 +2436,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>14092</t>
+          <t>13299</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>30581</t>
+          <t>30477</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2451,12 +2451,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>17,7%</t>
+          <t>16,71%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>38,41%</t>
+          <t>38,28%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2471,12 +2471,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15226</t>
+          <t>13901</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>32606</t>
+          <t>32238</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2486,12 +2486,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>30,73%</t>
+          <t>30,39%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2506,12 +2506,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33489</t>
+          <t>33677</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>57025</t>
+          <t>57458</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2521,12 +2521,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>18,03%</t>
+          <t>18,13%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>30,71%</t>
+          <t>30,94%</t>
         </is>
       </c>
     </row>
@@ -2549,12 +2549,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>40511</t>
+          <t>40604</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>58023</t>
+          <t>58807</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2564,12 +2564,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>51,01%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,89%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2584,12 +2584,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>66455</t>
+          <t>66413</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>85247</t>
+          <t>85979</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2599,12 +2599,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>62,64%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2619,12 +2619,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>113881</t>
+          <t>112047</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>139559</t>
+          <t>138860</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2634,12 +2634,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>61,32%</t>
+          <t>60,34%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>74,78%</t>
         </is>
       </c>
     </row>
@@ -2779,12 +2779,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>833</t>
+          <t>844</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7237</t>
+          <t>8197</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2799,7 +2799,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,3%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2814,12 +2814,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>739</t>
+          <t>740</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>8723</t>
+          <t>7939</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2834,7 +2834,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2849,12 +2849,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>2157</t>
+          <t>2514</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12112</t>
+          <t>11438</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2864,12 +2864,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,16%</t>
+          <t>0,18%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,88%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -2892,12 +2892,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4823</t>
+          <t>4808</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>18411</t>
+          <t>19278</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2912,7 +2912,7 @@
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2927,12 +2927,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>7911</t>
+          <t>7760</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>23840</t>
+          <t>22327</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2942,12 +2942,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>0,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,89%</t>
+          <t>2,71%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2962,12 +2962,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>14912</t>
+          <t>15778</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>34178</t>
+          <t>35961</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2977,12 +2977,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,08%</t>
+          <t>1,14%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>2,47%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -3005,12 +3005,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6685</t>
+          <t>6123</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>21291</t>
+          <t>22500</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -3020,12 +3020,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>1,2%</t>
+          <t>1,1%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,81%</t>
+          <t>4,03%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -3040,12 +3040,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>5294</t>
+          <t>5100</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>18871</t>
+          <t>18534</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -3055,12 +3055,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,64%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,29%</t>
+          <t>2,25%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -3075,12 +3075,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>14165</t>
+          <t>14828</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>34411</t>
+          <t>35058</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -3090,12 +3090,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,02%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,49%</t>
+          <t>2,54%</t>
         </is>
       </c>
     </row>
@@ -3118,12 +3118,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>117442</t>
+          <t>118088</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>159373</t>
+          <t>157516</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3133,12 +3133,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,03%</t>
+          <t>21,15%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>28,54%</t>
+          <t>28,21%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3153,12 +3153,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>205256</t>
+          <t>204759</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>256541</t>
+          <t>257856</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,91%</t>
+          <t>24,85%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>31,13%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3188,12 +3188,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>335936</t>
+          <t>336231</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>400741</t>
+          <t>397632</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,3%</t>
+          <t>24,32%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>28,99%</t>
+          <t>28,76%</t>
         </is>
       </c>
     </row>
@@ -3231,12 +3231,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>372893</t>
+          <t>373898</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>416360</t>
+          <t>417553</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3246,12 +3246,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,77%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>74,56%</t>
+          <t>74,77%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3266,12 +3266,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>539307</t>
+          <t>538589</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>590802</t>
+          <t>592110</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>65,45%</t>
+          <t>65,36%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>71,7%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3301,12 +3301,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>931911</t>
+          <t>932002</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>998117</t>
+          <t>998218</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>67,41%</t>
+          <t>67,42%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>72,2%</t>
+          <t>72,21%</t>
         </is>
       </c>
     </row>
@@ -3697,7 +3697,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>5472</t>
+          <t>5421</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3712,7 +3712,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>2,19%</t>
+          <t>2,17%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3767,7 +3767,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>6005</t>
+          <t>5457</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3782,7 +3782,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,83%</t>
         </is>
       </c>
     </row>
@@ -3805,12 +3805,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>931</t>
+          <t>922</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>8064</t>
+          <t>7721</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3825,7 +3825,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,23%</t>
+          <t>3,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3845,7 +3845,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7284</t>
+          <t>6703</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3860,7 +3860,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>1,78%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1959</t>
+          <t>1953</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>10940</t>
+          <t>11033</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3895,7 +3895,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>1,66%</t>
+          <t>1,67%</t>
         </is>
       </c>
     </row>
@@ -3923,7 +3923,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>6367</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -3938,7 +3938,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>2,53%</t>
+          <t>2,55%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -3958,7 +3958,7 @@
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>11047</t>
+          <t>10777</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -3973,7 +3973,7 @@
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,7%</t>
+          <t>2,63%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -3988,12 +3988,12 @@
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>963</t>
+          <t>964</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>10719</t>
+          <t>11200</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -4008,7 +4008,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,62%</t>
+          <t>1,7%</t>
         </is>
       </c>
     </row>
@@ -4031,12 +4031,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>68145</t>
+          <t>68280</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>101101</t>
+          <t>99261</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4046,12 +4046,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>27,27%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>40,46%</t>
+          <t>39,72%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4066,12 +4066,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>108061</t>
+          <t>106847</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>145762</t>
+          <t>144968</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4081,12 +4081,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>26,37%</t>
+          <t>26,07%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,37%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4101,12 +4101,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>185522</t>
+          <t>186927</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>235152</t>
+          <t>237796</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4116,12 +4116,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>28,12%</t>
+          <t>28,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>35,65%</t>
+          <t>36,05%</t>
         </is>
       </c>
     </row>
@@ -4144,12 +4144,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>143172</t>
+          <t>145001</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>176398</t>
+          <t>175601</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4159,12 +4159,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>57,29%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>70,59%</t>
+          <t>70,27%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4179,12 +4179,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>258993</t>
+          <t>260108</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>297655</t>
+          <t>298940</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4194,12 +4194,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,47%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>72,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4214,12 +4214,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>414680</t>
+          <t>412990</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>462753</t>
+          <t>464410</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4229,12 +4229,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>62,86%</t>
+          <t>62,6%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>70,15%</t>
+          <t>70,4%</t>
         </is>
       </c>
     </row>
@@ -4379,7 +4379,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>5527</t>
+          <t>4752</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4394,7 +4394,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>1,44%</t>
+          <t>1,24%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4449,7 +4449,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>4599</t>
+          <t>4595</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4522,12 +4522,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>2824</t>
+          <t>2800</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>13941</t>
+          <t>15249</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4537,12 +4537,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,63%</t>
+          <t>0,62%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>3,38%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4557,12 +4557,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>2861</t>
+          <t>2854</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>13708</t>
+          <t>15339</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4577,7 +4577,7 @@
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>1,64%</t>
+          <t>1,84%</t>
         </is>
       </c>
     </row>
@@ -4600,12 +4600,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>3056</t>
+          <t>3077</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16086</t>
+          <t>16311</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -4620,7 +4620,7 @@
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>4,19%</t>
+          <t>4,25%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -4635,12 +4635,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>1928</t>
+          <t>1914</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>11876</t>
+          <t>11758</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -4650,12 +4650,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>0,43%</t>
+          <t>0,42%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -4670,12 +4670,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>7632</t>
+          <t>7736</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>23140</t>
+          <t>24777</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,93%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>2,77%</t>
+          <t>2,97%</t>
         </is>
       </c>
     </row>
@@ -4713,12 +4713,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>107867</t>
+          <t>108061</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>145856</t>
+          <t>147430</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4728,12 +4728,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>38,03%</t>
+          <t>38,44%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4748,12 +4748,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>134825</t>
+          <t>133455</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>177887</t>
+          <t>173525</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4763,12 +4763,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>29,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>39,44%</t>
+          <t>38,47%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4783,12 +4783,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>256993</t>
+          <t>254136</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>312048</t>
+          <t>311032</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4798,12 +4798,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>30,79%</t>
+          <t>30,45%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>37,39%</t>
+          <t>37,27%</t>
         </is>
       </c>
     </row>
@@ -4826,12 +4826,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>229190</t>
+          <t>227278</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>266538</t>
+          <t>266330</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4841,12 +4841,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>59,76%</t>
+          <t>59,26%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,5%</t>
+          <t>69,45%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4861,12 +4861,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>261696</t>
+          <t>265329</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>305040</t>
+          <t>304855</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4876,12 +4876,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>58,02%</t>
+          <t>58,82%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,63%</t>
+          <t>67,59%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4896,12 +4896,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>503451</t>
+          <t>502121</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>557802</t>
+          <t>559317</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4911,12 +4911,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,32%</t>
+          <t>60,16%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>66,84%</t>
+          <t>67,02%</t>
         </is>
       </c>
     </row>
@@ -5174,7 +5174,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>4617</t>
+          <t>5533</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5189,7 +5189,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>6,65%</t>
+          <t>7,97%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5204,12 +5204,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>2854</t>
+          <t>2791</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>14807</t>
+          <t>15509</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5219,12 +5219,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,44%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>12,95%</t>
+          <t>13,57%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5239,12 +5239,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>2848</t>
+          <t>3147</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>15498</t>
+          <t>15821</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5254,12 +5254,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,71%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>8,43%</t>
+          <t>8,61%</t>
         </is>
       </c>
     </row>
@@ -5282,12 +5282,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>956</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>8002</t>
+          <t>8967</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -5297,12 +5297,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>1,33%</t>
+          <t>1,38%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>12,91%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -5317,12 +5317,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>2132</t>
+          <t>2267</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>12812</t>
+          <t>12799</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -5332,12 +5332,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>1,98%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,2%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -5352,12 +5352,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>4985</t>
+          <t>4932</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>17492</t>
+          <t>16994</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -5367,12 +5367,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>2,71%</t>
+          <t>2,68%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>9,52%</t>
+          <t>9,25%</t>
         </is>
       </c>
     </row>
@@ -5395,12 +5395,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>24819</t>
+          <t>26247</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>42384</t>
+          <t>42317</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5410,12 +5410,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>37,79%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>61,02%</t>
+          <t>60,92%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5430,12 +5430,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>15588</t>
+          <t>14976</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>33405</t>
+          <t>34104</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5445,12 +5445,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,64%</t>
+          <t>13,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>29,22%</t>
+          <t>29,84%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5465,12 +5465,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>45531</t>
+          <t>45895</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>70806</t>
+          <t>72827</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5480,12 +5480,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>24,78%</t>
+          <t>24,97%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>38,53%</t>
+          <t>39,63%</t>
         </is>
       </c>
     </row>
@@ -5508,12 +5508,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>23588</t>
+          <t>23338</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40288</t>
+          <t>39793</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5523,12 +5523,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>33,6%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>58,0%</t>
+          <t>57,29%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5543,12 +5543,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>66030</t>
+          <t>66005</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>86737</t>
+          <t>87783</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5558,12 +5558,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>57,74%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>75,88%</t>
+          <t>76,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5578,12 +5578,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>94989</t>
+          <t>92942</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>123149</t>
+          <t>121238</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5593,12 +5593,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>51,69%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,01%</t>
+          <t>65,97%</t>
         </is>
       </c>
     </row>
@@ -5743,7 +5743,7 @@
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>7012</t>
+          <t>6309</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5758,7 +5758,7 @@
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,0%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5813,7 +5813,7 @@
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>6457</t>
+          <t>6898</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5828,7 +5828,7 @@
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,38%</t>
+          <t>0,41%</t>
         </is>
       </c>
     </row>
@@ -5851,12 +5851,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>1007</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>8809</t>
+          <t>9880</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5866,12 +5866,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>1,41%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5886,12 +5886,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>8875</t>
+          <t>8957</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>26632</t>
+          <t>26491</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5901,12 +5901,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>0,91%</t>
+          <t>0,92%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>2,73%</t>
+          <t>2,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5921,12 +5921,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>11792</t>
+          <t>12007</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>30407</t>
+          <t>33346</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5936,12 +5936,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>0,7%</t>
+          <t>0,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>1,99%</t>
         </is>
       </c>
     </row>
@@ -5964,12 +5964,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>6509</t>
+          <t>6300</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>22791</t>
+          <t>22204</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -5979,12 +5979,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>0,93%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>3,24%</t>
+          <t>3,16%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -5999,12 +5999,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>8218</t>
+          <t>8764</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>24475</t>
+          <t>24586</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -6014,12 +6014,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>0,84%</t>
+          <t>0,9%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>2,51%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -6034,12 +6034,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>17430</t>
+          <t>17820</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>39562</t>
+          <t>40912</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -6049,12 +6049,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>1,04%</t>
+          <t>1,06%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>2,36%</t>
+          <t>2,44%</t>
         </is>
       </c>
     </row>
@@ -6077,12 +6077,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>221041</t>
+          <t>219861</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>274310</t>
+          <t>270510</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6092,12 +6092,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,45%</t>
+          <t>31,28%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,03%</t>
+          <t>38,49%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6112,12 +6112,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>274300</t>
+          <t>275375</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>333812</t>
+          <t>333040</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>28,13%</t>
+          <t>28,24%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>34,23%</t>
+          <t>34,15%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>512585</t>
+          <t>511136</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>593907</t>
+          <t>589454</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,55%</t>
+          <t>30,46%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>35,39%</t>
+          <t>35,13%</t>
         </is>
       </c>
     </row>
@@ -6190,12 +6190,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>411648</t>
+          <t>412223</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>464856</t>
+          <t>465718</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6205,12 +6205,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>58,57%</t>
+          <t>58,65%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>66,14%</t>
+          <t>66,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6225,12 +6225,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>607108</t>
+          <t>611122</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>670468</t>
+          <t>668667</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,26%</t>
+          <t>62,67%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,75%</t>
+          <t>68,57%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1036950</t>
+          <t>1037870</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1119659</t>
+          <t>1119257</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>61,85%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>66,72%</t>
+          <t>66,7%</t>
         </is>
       </c>
     </row>
@@ -6656,7 +6656,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>6081</t>
+          <t>6014</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6671,7 +6671,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>4,43%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6691,7 +6691,7 @@
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>5293</t>
+          <t>7706</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6706,7 +6706,7 @@
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>2,37%</t>
+          <t>3,45%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6721,12 +6721,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>806</t>
+          <t>810</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>8604</t>
+          <t>8153</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6741,7 +6741,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>2,39%</t>
+          <t>2,26%</t>
         </is>
       </c>
     </row>
@@ -6804,7 +6804,7 @@
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>9905</t>
+          <t>7962</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6819,7 +6819,7 @@
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>4,44%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6839,7 +6839,7 @@
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8457</t>
+          <t>7543</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6854,7 +6854,7 @@
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,35%</t>
+          <t>2,09%</t>
         </is>
       </c>
     </row>
@@ -6882,7 +6882,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5545</t>
+          <t>5150</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -6897,7 +6897,7 @@
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,04%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -6952,7 +6952,7 @@
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>5151</t>
+          <t>6145</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -6967,7 +6967,7 @@
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>1,43%</t>
+          <t>1,71%</t>
         </is>
       </c>
     </row>
@@ -6990,12 +6990,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>27790</t>
+          <t>27390</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>47902</t>
+          <t>48149</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7005,12 +7005,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>20,25%</t>
+          <t>19,96%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,91%</t>
+          <t>35,09%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7025,12 +7025,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>41900</t>
+          <t>42219</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>69436</t>
+          <t>68222</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7040,12 +7040,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>31,12%</t>
+          <t>30,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7060,12 +7060,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>74731</t>
+          <t>76012</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>110202</t>
+          <t>109878</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7075,12 +7075,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>30,58%</t>
+          <t>30,49%</t>
         </is>
       </c>
     </row>
@@ -7103,12 +7103,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>86720</t>
+          <t>86555</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>107799</t>
+          <t>107547</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>63,2%</t>
+          <t>63,08%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,57%</t>
+          <t>78,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7138,12 +7138,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>149991</t>
+          <t>151638</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>177663</t>
+          <t>178087</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7153,12 +7153,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>67,22%</t>
+          <t>67,96%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>79,62%</t>
+          <t>79,81%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7173,12 +7173,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>242493</t>
+          <t>243206</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>278930</t>
+          <t>278499</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7188,12 +7188,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,29%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,41%</t>
+          <t>77,29%</t>
         </is>
       </c>
     </row>
@@ -7338,7 +7338,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>6766</t>
+          <t>6707</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7353,7 +7353,7 @@
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,01%</t>
+          <t>1,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7408,7 +7408,7 @@
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>6660</t>
+          <t>6741</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7423,7 +7423,7 @@
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>0,93%</t>
         </is>
       </c>
     </row>
@@ -7446,12 +7446,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3341</t>
+          <t>3008</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>14303</t>
+          <t>13814</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,99%</t>
+          <t>0,89%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>4,25%</t>
+          <t>4,1%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7481,12 +7481,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>4481</t>
+          <t>4535</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18910</t>
+          <t>18774</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7496,12 +7496,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>1,16%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>4,88%</t>
+          <t>4,84%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7516,12 +7516,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>10754</t>
+          <t>10714</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28160</t>
+          <t>27692</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7531,12 +7531,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>1,49%</t>
+          <t>1,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>3,89%</t>
+          <t>3,82%</t>
         </is>
       </c>
     </row>
@@ -7559,12 +7559,12 @@
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8841</t>
+          <t>9410</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>27166</t>
+          <t>28302</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,63%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>8,41%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -7594,12 +7594,12 @@
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>6332</t>
+          <t>6517</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>20524</t>
+          <t>21671</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -7609,12 +7609,12 @@
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,63%</t>
+          <t>1,68%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>5,3%</t>
+          <t>5,59%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -7629,12 +7629,12 @@
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18138</t>
+          <t>19284</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>41686</t>
+          <t>43349</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -7644,12 +7644,12 @@
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>2,5%</t>
+          <t>2,66%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,99%</t>
         </is>
       </c>
     </row>
@@ -7672,12 +7672,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72924</t>
+          <t>73498</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>107564</t>
+          <t>106505</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7687,12 +7687,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,66%</t>
+          <t>21,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>31,96%</t>
+          <t>31,64%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7707,12 +7707,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>104192</t>
+          <t>102052</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>140988</t>
+          <t>140680</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7722,12 +7722,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>26,88%</t>
+          <t>26,33%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>36,38%</t>
+          <t>36,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7742,12 +7742,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>186477</t>
+          <t>184811</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>233568</t>
+          <t>236243</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7757,12 +7757,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>25,75%</t>
+          <t>25,52%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>32,25%</t>
+          <t>32,62%</t>
         </is>
       </c>
     </row>
@@ -7785,12 +7785,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>202512</t>
+          <t>202711</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>240240</t>
+          <t>239489</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7800,12 +7800,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>60,22%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>71,37%</t>
+          <t>71,15%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7820,12 +7820,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>223799</t>
+          <t>222926</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>261692</t>
+          <t>264099</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7835,12 +7835,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>57,74%</t>
+          <t>57,52%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>67,52%</t>
+          <t>68,14%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7855,12 +7855,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>437057</t>
+          <t>440682</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>489626</t>
+          <t>492094</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7870,12 +7870,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>60,35%</t>
+          <t>60,85%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,95%</t>
         </is>
       </c>
     </row>
@@ -8055,7 +8055,7 @@
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>5028</t>
+          <t>4906</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>3,75%</t>
+          <t>3,66%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8090,7 +8090,7 @@
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>3867</t>
+          <t>5415</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8105,7 +8105,7 @@
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>1,86%</t>
+          <t>2,6%</t>
         </is>
       </c>
     </row>
@@ -8133,7 +8133,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6264</t>
+          <t>6831</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8148,7 +8148,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>8,48%</t>
+          <t>9,24%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8163,12 +8163,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9272</t>
+          <t>9514</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>26713</t>
+          <t>27036</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8178,12 +8178,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>6,91%</t>
+          <t>7,09%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>20,14%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8198,12 +8198,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>10820</t>
+          <t>10591</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>28478</t>
+          <t>29247</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8213,12 +8213,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,09%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,68%</t>
+          <t>14,05%</t>
         </is>
       </c>
     </row>
@@ -8241,12 +8241,12 @@
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>3824</t>
+          <t>4037</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>16323</t>
+          <t>16646</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -8256,12 +8256,12 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5,17%</t>
+          <t>5,46%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,53%</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
@@ -8276,12 +8276,12 @@
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6726</t>
+          <t>6420</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>20384</t>
+          <t>20748</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -8291,12 +8291,12 @@
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>5,01%</t>
+          <t>4,78%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>15,19%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -8311,12 +8311,12 @@
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>13250</t>
+          <t>13009</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>31119</t>
+          <t>30927</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -8326,12 +8326,12 @@
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>6,37%</t>
+          <t>6,25%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>14,86%</t>
         </is>
       </c>
     </row>
@@ -8354,12 +8354,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>7689</t>
+          <t>7099</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>22227</t>
+          <t>21173</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8369,12 +8369,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>10,41%</t>
+          <t>9,61%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>30,08%</t>
+          <t>28,65%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8389,12 +8389,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>18494</t>
+          <t>17849</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>37715</t>
+          <t>36641</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8404,12 +8404,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>13,78%</t>
+          <t>13,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>28,1%</t>
+          <t>27,3%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8424,12 +8424,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>29729</t>
+          <t>29682</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>52917</t>
+          <t>52284</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8439,12 +8439,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>14,28%</t>
+          <t>14,26%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>25,43%</t>
+          <t>25,12%</t>
         </is>
       </c>
     </row>
@@ -8467,12 +8467,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>41410</t>
+          <t>40189</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>57762</t>
+          <t>57439</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8482,12 +8482,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>56,04%</t>
+          <t>54,39%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>78,17%</t>
+          <t>77,73%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8502,12 +8502,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>66655</t>
+          <t>65368</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>89504</t>
+          <t>89385</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8517,12 +8517,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>49,66%</t>
+          <t>48,7%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>66,59%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8537,12 +8537,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>112043</t>
+          <t>113714</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>142262</t>
+          <t>142883</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8552,12 +8552,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>53,84%</t>
+          <t>54,64%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>68,36%</t>
+          <t>68,65%</t>
         </is>
       </c>
     </row>
@@ -8697,12 +8697,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>944</t>
+          <t>903</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9332</t>
+          <t>8290</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8712,12 +8712,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,17%</t>
+          <t>0,16%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,51%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8737,7 +8737,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>7659</t>
+          <t>7781</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8752,7 +8752,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>1,03%</t>
+          <t>1,04%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8767,12 +8767,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>1901</t>
+          <t>1855</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>13043</t>
+          <t>12325</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8782,12 +8782,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,15%</t>
+          <t>0,14%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>1,01%</t>
+          <t>0,95%</t>
         </is>
       </c>
     </row>
@@ -8810,12 +8810,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4655</t>
+          <t>4451</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>17087</t>
+          <t>17039</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8825,12 +8825,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>0,85%</t>
+          <t>0,81%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>3,12%</t>
+          <t>3,11%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8845,12 +8845,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>19523</t>
+          <t>18797</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42872</t>
+          <t>42272</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8860,12 +8860,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>2,62%</t>
+          <t>2,52%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>5,76%</t>
+          <t>5,67%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8880,12 +8880,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>26538</t>
+          <t>26983</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>52568</t>
+          <t>52294</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8895,12 +8895,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>2,05%</t>
+          <t>2,09%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>4,07%</t>
+          <t>4,05%</t>
         </is>
       </c>
     </row>
@@ -8923,12 +8923,12 @@
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>16918</t>
+          <t>16232</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>39693</t>
+          <t>38947</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -8938,12 +8938,12 @@
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,09%</t>
+          <t>2,96%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,25%</t>
+          <t>7,11%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -8958,12 +8958,12 @@
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>16397</t>
+          <t>15483</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>37045</t>
+          <t>34635</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -8973,12 +8973,12 @@
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>2,2%</t>
+          <t>2,08%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>4,97%</t>
+          <t>4,65%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -8993,12 +8993,12 @@
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>37904</t>
+          <t>37230</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>67188</t>
+          <t>66694</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -9008,12 +9008,12 @@
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,93%</t>
+          <t>2,88%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,2%</t>
+          <t>5,16%</t>
         </is>
       </c>
     </row>
@@ -9036,12 +9036,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>117729</t>
+          <t>117370</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>160906</t>
+          <t>160561</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9051,12 +9051,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>21,5%</t>
+          <t>21,43%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9071,12 +9071,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>181734</t>
+          <t>178924</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>229860</t>
+          <t>228358</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9086,12 +9086,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>24,4%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>30,86%</t>
+          <t>30,65%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>310415</t>
+          <t>310047</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>378226</t>
+          <t>374778</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9121,12 +9121,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>23,99%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>29,26%</t>
+          <t>28,99%</t>
         </is>
       </c>
     </row>
@@ -9149,12 +9149,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>348131</t>
+          <t>347001</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>393296</t>
+          <t>391303</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9164,12 +9164,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>63,56%</t>
+          <t>63,36%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,81%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9184,12 +9184,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>456347</t>
+          <t>459870</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>510424</t>
+          <t>513052</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9199,12 +9199,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,26%</t>
+          <t>61,73%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,52%</t>
+          <t>68,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>817245</t>
+          <t>819658</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>892280</t>
+          <t>889650</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9234,12 +9234,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>63,22%</t>
+          <t>63,41%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,03%</t>
+          <t>68,82%</t>
         </is>
       </c>
     </row>
@@ -9605,7 +9605,7 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>819</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
@@ -9615,12 +9615,12 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4457</t>
+          <t>4365</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
@@ -9630,7 +9630,7 @@
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>3,37%</t>
+          <t>3,1%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9675,7 +9675,7 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>759</t>
+          <t>819</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
@@ -9685,7 +9685,7 @@
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>3817</t>
+          <t>4834</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9700,7 +9700,7 @@
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>1,09%</t>
+          <t>1,27%</t>
         </is>
       </c>
     </row>
@@ -9718,7 +9718,7 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>760</t>
+          <t>817</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
@@ -9728,12 +9728,12 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>3972</t>
+          <t>5032</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
@@ -9743,7 +9743,7 @@
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>3,0%</t>
+          <t>3,57%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9753,32 +9753,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>2955</t>
+          <t>3645</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>1133</t>
+          <t>1446</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>7566</t>
+          <t>8651</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>1,35%</t>
+          <t>1,52%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>0,52%</t>
+          <t>0,6%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>3,46%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9788,32 +9788,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>3715</t>
+          <t>4462</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>1416</t>
+          <t>1915</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>8118</t>
+          <t>10487</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>1,06%</t>
+          <t>1,17%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>0,4%</t>
+          <t>0,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>2,31%</t>
+          <t>2,76%</t>
         </is>
       </c>
     </row>
@@ -9831,32 +9831,32 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>2253</t>
+          <t>2276</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>632</t>
+          <t>610</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>5888</t>
+          <t>6254</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>1,7%</t>
+          <t>1,62%</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>0,48%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,44%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -9866,32 +9866,32 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>1728</t>
+          <t>1810</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>312</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>5771</t>
+          <t>5612</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0,79%</t>
+          <t>0,76%</t>
         </is>
       </c>
       <c r="O6" s="2" t="inlineStr">
         <is>
-          <t>0,14%</t>
+          <t>0,13%</t>
         </is>
       </c>
       <c r="P6" s="2" t="inlineStr">
         <is>
-          <t>2,64%</t>
+          <t>2,34%</t>
         </is>
       </c>
       <c r="Q6" s="2" t="inlineStr">
@@ -9901,32 +9901,32 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>3981</t>
+          <t>4086</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>1554</t>
+          <t>1421</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>8922</t>
+          <t>9413</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
         <is>
-          <t>1,13%</t>
+          <t>1,07%</t>
         </is>
       </c>
       <c r="V6" s="2" t="inlineStr">
         <is>
-          <t>0,44%</t>
+          <t>0,37%</t>
         </is>
       </c>
       <c r="W6" s="2" t="inlineStr">
         <is>
-          <t>2,54%</t>
+          <t>2,47%</t>
         </is>
       </c>
     </row>
@@ -9944,32 +9944,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27959</t>
+          <t>28790</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>18736</t>
+          <t>18682</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>41418</t>
+          <t>40745</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,45%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,17%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>31,32%</t>
+          <t>28,94%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -9979,32 +9979,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>38871</t>
+          <t>41245</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31043</t>
+          <t>33365</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>48414</t>
+          <t>52124</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>17,75%</t>
+          <t>17,21%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>14,18%</t>
+          <t>13,92%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,11%</t>
+          <t>21,75%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10014,32 +10014,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>66830</t>
+          <t>70035</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>53422</t>
+          <t>56620</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>82481</t>
+          <t>84731</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>19,03%</t>
+          <t>18,41%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>14,88%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>23,49%</t>
+          <t>22,27%</t>
         </is>
       </c>
     </row>
@@ -10057,32 +10057,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>100506</t>
+          <t>108093</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>87211</t>
+          <t>96080</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>110070</t>
+          <t>117935</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>76,77%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>68,24%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,24%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10092,32 +10092,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>175414</t>
+          <t>192969</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>164721</t>
+          <t>181891</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>182942</t>
+          <t>201655</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>80,11%</t>
+          <t>80,51%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>75,23%</t>
+          <t>75,89%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>84,14%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10127,32 +10127,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>275920</t>
+          <t>301062</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>260091</t>
+          <t>285164</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>290306</t>
+          <t>314970</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>78,56%</t>
+          <t>79,13%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>74,95%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,79%</t>
         </is>
       </c>
     </row>
@@ -10170,17 +10170,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>132237</t>
+          <t>140796</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>132237</t>
+          <t>140796</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>132237</t>
+          <t>140796</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10205,17 +10205,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>218968</t>
+          <t>239669</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>218968</t>
+          <t>239669</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>218968</t>
+          <t>239669</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10240,17 +10240,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>351205</t>
+          <t>380464</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>351205</t>
+          <t>380464</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>351205</t>
+          <t>380464</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10287,32 +10287,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>3879</t>
+          <t>4873</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>1315</t>
+          <t>1722</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>9680</t>
+          <t>11098</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>0,96%</t>
+          <t>1,13%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>0,33%</t>
+          <t>0,4%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2,4%</t>
+          <t>2,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10322,32 +10322,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>880</t>
+          <t>1371</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>9176</t>
+          <t>9138</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>0,57%</t>
+          <t>0,79%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>0,13%</t>
+          <t>0,27%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>1,4%</t>
+          <t>1,82%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10357,32 +10357,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>7612</t>
+          <t>8845</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>3034</t>
+          <t>4341</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>14556</t>
+          <t>16109</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>0,72%</t>
+          <t>0,95%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>0,29%</t>
+          <t>0,46%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>1,37%</t>
+          <t>1,72%</t>
         </is>
       </c>
     </row>
@@ -10400,32 +10400,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>7006</t>
+          <t>8233</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>3053</t>
+          <t>3938</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>13639</t>
+          <t>16255</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>1,73%</t>
+          <t>1,91%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>0,76%</t>
+          <t>0,91%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>3,38%</t>
+          <t>3,77%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10435,32 +10435,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>11170</t>
+          <t>12160</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>3769</t>
+          <t>7295</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>20094</t>
+          <t>20748</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>1,71%</t>
+          <t>2,42%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>0,58%</t>
+          <t>1,45%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>3,07%</t>
+          <t>4,12%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10470,32 +10470,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>18177</t>
+          <t>20393</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>8310</t>
+          <t>13738</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>28354</t>
+          <t>30302</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>1,72%</t>
+          <t>2,18%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>0,78%</t>
+          <t>1,47%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>2,68%</t>
+          <t>3,24%</t>
         </is>
       </c>
     </row>
@@ -10513,17 +10513,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>15469</t>
+          <t>16541</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>8161</t>
+          <t>8322</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>30762</t>
+          <t>31724</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10533,12 +10533,12 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>2,02%</t>
+          <t>1,93%</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>7,62%</t>
+          <t>7,35%</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
@@ -10548,32 +10548,32 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>24665</t>
+          <t>26794</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>8042</t>
+          <t>17306</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>41599</t>
+          <t>37294</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>3,77%</t>
+          <t>5,33%</t>
         </is>
       </c>
       <c r="O12" s="2" t="inlineStr">
         <is>
-          <t>1,23%</t>
+          <t>3,44%</t>
         </is>
       </c>
       <c r="P12" s="2" t="inlineStr">
         <is>
-          <t>6,35%</t>
+          <t>7,41%</t>
         </is>
       </c>
       <c r="Q12" s="2" t="inlineStr">
@@ -10583,32 +10583,32 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>40134</t>
+          <t>43334</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>18386</t>
+          <t>30791</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>57231</t>
+          <t>61999</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
         <is>
-          <t>3,79%</t>
+          <t>4,64%</t>
         </is>
       </c>
       <c r="V12" s="2" t="inlineStr">
         <is>
-          <t>1,74%</t>
+          <t>3,29%</t>
         </is>
       </c>
       <c r="W12" s="2" t="inlineStr">
         <is>
-          <t>5,41%</t>
+          <t>6,63%</t>
         </is>
       </c>
     </row>
@@ -10626,32 +10626,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>79924</t>
+          <t>85860</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>62601</t>
+          <t>67280</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>102127</t>
+          <t>106227</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>19,79%</t>
+          <t>19,9%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,5%</t>
+          <t>15,59%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>25,29%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10661,32 +10661,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>86546</t>
+          <t>95669</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>36151</t>
+          <t>79537</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>133717</t>
+          <t>112179</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>19,02%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>5,52%</t>
+          <t>15,81%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,42%</t>
+          <t>22,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10696,32 +10696,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>166470</t>
+          <t>181529</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>82819</t>
+          <t>157563</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>218319</t>
+          <t>204673</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>15,72%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>7,82%</t>
+          <t>16,86%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,62%</t>
+          <t>21,9%</t>
         </is>
       </c>
     </row>
@@ -10739,32 +10739,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>297579</t>
+          <t>315976</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>275425</t>
+          <t>291709</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>317914</t>
+          <t>336096</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>73,68%</t>
+          <t>73,23%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>68,2%</t>
+          <t>67,61%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,72%</t>
+          <t>77,89%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10774,32 +10774,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>528835</t>
+          <t>364423</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>463323</t>
+          <t>345976</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>603677</t>
+          <t>382896</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>80,74%</t>
+          <t>72,45%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>70,74%</t>
+          <t>68,78%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>76,12%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10809,32 +10809,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>826414</t>
+          <t>680399</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>760995</t>
+          <t>654096</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>949477</t>
+          <t>709121</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>71,87%</t>
+          <t>69,99%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>89,67%</t>
+          <t>75,88%</t>
         </is>
       </c>
     </row>
@@ -10852,17 +10852,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>403857</t>
+          <t>431483</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>403857</t>
+          <t>431483</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>403857</t>
+          <t>431483</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10887,17 +10887,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>654950</t>
+          <t>503018</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>654950</t>
+          <t>503018</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>654950</t>
+          <t>503018</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10922,17 +10922,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1058807</t>
+          <t>934501</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1058807</t>
+          <t>934501</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1058807</t>
+          <t>934501</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11082,32 +11082,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>11943</t>
+          <t>11414</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>6161</t>
+          <t>5913</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>21201</t>
+          <t>19051</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>8,57%</t>
+          <t>7,16%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>4,42%</t>
+          <t>3,71%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>11,96%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11117,32 +11117,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>14899</t>
+          <t>16951</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>9677</t>
+          <t>10959</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>23805</t>
+          <t>25701</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>8,7%</t>
+          <t>8,92%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>5,65%</t>
+          <t>5,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>13,91%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11152,32 +11152,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>26842</t>
+          <t>28366</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>17869</t>
+          <t>19377</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>37643</t>
+          <t>38778</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>8,64%</t>
+          <t>8,12%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,55%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>12,12%</t>
+          <t>11,1%</t>
         </is>
       </c>
     </row>
@@ -11195,17 +11195,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>16234</t>
+          <t>18551</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>9935</t>
+          <t>11285</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>26781</t>
+          <t>30602</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11215,7 +11215,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>7,13%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
@@ -11230,32 +11230,32 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>11209</t>
+          <t>12293</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>6169</t>
+          <t>7102</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>18271</t>
+          <t>19799</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>6,55%</t>
+          <t>6,47%</t>
         </is>
       </c>
       <c r="O18" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>3,74%</t>
         </is>
       </c>
       <c r="P18" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="Q18" s="2" t="inlineStr">
@@ -11265,32 +11265,32 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>27443</t>
+          <t>30845</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>18595</t>
+          <t>21717</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>37673</t>
+          <t>43753</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>8,83%</t>
         </is>
       </c>
       <c r="V18" s="2" t="inlineStr">
         <is>
-          <t>5,99%</t>
+          <t>6,22%</t>
         </is>
       </c>
       <c r="W18" s="2" t="inlineStr">
         <is>
-          <t>12,13%</t>
+          <t>12,52%</t>
         </is>
       </c>
     </row>
@@ -11308,32 +11308,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>22012</t>
+          <t>23211</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>13309</t>
+          <t>14257</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33868</t>
+          <t>36601</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>15,79%</t>
+          <t>14,57%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>9,55%</t>
+          <t>8,95%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>22,97%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11343,32 +11343,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>43510</t>
+          <t>44481</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>33416</t>
+          <t>34526</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>56638</t>
+          <t>56057</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>25,42%</t>
+          <t>23,4%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>33,09%</t>
+          <t>29,49%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11378,32 +11378,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>65522</t>
+          <t>67693</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>51920</t>
+          <t>54156</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>83065</t>
+          <t>85448</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>21,1%</t>
+          <t>19,37%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>15,5%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>24,45%</t>
         </is>
       </c>
     </row>
@@ -11421,32 +11421,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>89231</t>
+          <t>106138</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>74509</t>
+          <t>92334</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>101241</t>
+          <t>119655</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>66,62%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>53,44%</t>
+          <t>57,96%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>72,62%</t>
+          <t>75,11%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11456,32 +11456,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>101557</t>
+          <t>116370</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>89818</t>
+          <t>103772</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>114230</t>
+          <t>128758</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>59,33%</t>
+          <t>61,22%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>52,47%</t>
+          <t>54,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,73%</t>
+          <t>67,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11491,32 +11491,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>190788</t>
+          <t>222508</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>173369</t>
+          <t>204377</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>209060</t>
+          <t>241030</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>63,68%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>55,82%</t>
+          <t>58,49%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,31%</t>
+          <t>68,98%</t>
         </is>
       </c>
     </row>
@@ -11534,17 +11534,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>139420</t>
+          <t>159315</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>139420</t>
+          <t>159315</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>139420</t>
+          <t>159315</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11569,17 +11569,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>171176</t>
+          <t>190096</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>171176</t>
+          <t>190096</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>171176</t>
+          <t>190096</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11604,17 +11604,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>310596</t>
+          <t>349411</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>310596</t>
+          <t>349411</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>310596</t>
+          <t>349411</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11651,32 +11651,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>4638</t>
+          <t>5693</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>1756</t>
+          <t>2136</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>10467</t>
+          <t>11982</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>0,69%</t>
+          <t>0,78%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>0,26%</t>
+          <t>0,29%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>1,55%</t>
+          <t>1,64%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11686,32 +11686,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>3733</t>
+          <t>3972</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>923</t>
+          <t>1380</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>9035</t>
+          <t>8955</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>0,36%</t>
+          <t>0,43%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>0,09%</t>
+          <t>0,15%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>0,86%</t>
+          <t>0,96%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11721,32 +11721,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>8371</t>
+          <t>9665</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4100</t>
+          <t>5013</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>15785</t>
+          <t>17232</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>0,49%</t>
+          <t>0,58%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>0,24%</t>
+          <t>0,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>0,92%</t>
+          <t>1,04%</t>
         </is>
       </c>
     </row>
@@ -11764,32 +11764,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>19709</t>
+          <t>20465</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>12485</t>
+          <t>13186</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>30091</t>
+          <t>31178</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>2,92%</t>
+          <t>2,8%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>1,85%</t>
+          <t>1,8%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>4,45%</t>
+          <t>4,26%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11799,32 +11799,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>29024</t>
+          <t>32757</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>13111</t>
+          <t>24385</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>41370</t>
+          <t>46520</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>2,78%</t>
+          <t>3,51%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>1,25%</t>
+          <t>2,61%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>3,96%</t>
+          <t>4,99%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11834,32 +11834,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>48734</t>
+          <t>53221</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>31142</t>
+          <t>41082</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>63669</t>
+          <t>67684</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>2,83%</t>
+          <t>3,2%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>1,81%</t>
+          <t>2,47%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>3,7%</t>
+          <t>4,07%</t>
         </is>
       </c>
     </row>
@@ -11877,32 +11877,32 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>33956</t>
+          <t>37368</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>23477</t>
+          <t>26419</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>51729</t>
+          <t>56339</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>5,03%</t>
+          <t>5,11%</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>3,48%</t>
+          <t>3,61%</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>7,66%</t>
+          <t>7,7%</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
@@ -11912,32 +11912,32 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>37602</t>
+          <t>40897</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>17523</t>
+          <t>29545</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>53696</t>
+          <t>54775</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>3,6%</t>
+          <t>4,38%</t>
         </is>
       </c>
       <c r="O24" s="2" t="inlineStr">
         <is>
-          <t>1,68%</t>
+          <t>3,17%</t>
         </is>
       </c>
       <c r="P24" s="2" t="inlineStr">
         <is>
-          <t>5,14%</t>
+          <t>5,87%</t>
         </is>
       </c>
       <c r="Q24" s="2" t="inlineStr">
@@ -11947,32 +11947,32 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>71558</t>
+          <t>78265</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>46367</t>
+          <t>60275</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>91606</t>
+          <t>99885</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
         <is>
-          <t>4,16%</t>
+          <t>4,7%</t>
         </is>
       </c>
       <c r="V24" s="2" t="inlineStr">
         <is>
-          <t>2,69%</t>
+          <t>3,62%</t>
         </is>
       </c>
       <c r="W24" s="2" t="inlineStr">
         <is>
-          <t>5,32%</t>
+          <t>6,0%</t>
         </is>
       </c>
     </row>
@@ -11990,32 +11990,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>129895</t>
+          <t>137862</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>106742</t>
+          <t>113869</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>153293</t>
+          <t>162115</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>18,84%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,56%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12025,32 +12025,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>168928</t>
+          <t>181395</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>95308</t>
+          <t>159697</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>218536</t>
+          <t>201854</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>16,16%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>9,12%</t>
+          <t>17,12%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>20,91%</t>
+          <t>21,64%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12060,32 +12060,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>298822</t>
+          <t>319257</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>196163</t>
+          <t>289483</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>353698</t>
+          <t>352467</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>17,37%</t>
+          <t>19,18%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>11,4%</t>
+          <t>17,39%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>20,56%</t>
+          <t>21,18%</t>
         </is>
       </c>
     </row>
@@ -12103,32 +12103,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>487316</t>
+          <t>530207</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>459560</t>
+          <t>502790</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>513456</t>
+          <t>557073</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>72,14%</t>
+          <t>72,47%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>68,03%</t>
+          <t>68,73%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>76,01%</t>
+          <t>76,15%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12138,32 +12138,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>805806</t>
+          <t>673762</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>737789</t>
+          <t>648984</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>914456</t>
+          <t>698440</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>72,23%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>70,6%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>74,88%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12173,32 +12173,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>1293122</t>
+          <t>1203969</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1224116</t>
+          <t>1164191</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1438063</t>
+          <t>1239581</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>75,15%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>71,14%</t>
+          <t>69,95%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>74,48%</t>
         </is>
       </c>
     </row>
@@ -12216,17 +12216,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>675514</t>
+          <t>731594</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>675514</t>
+          <t>731594</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>675514</t>
+          <t>731594</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12251,17 +12251,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>1045094</t>
+          <t>932783</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>1045094</t>
+          <t>932783</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>1045094</t>
+          <t>932783</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12286,17 +12286,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1720608</t>
+          <t>1664377</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1720608</t>
+          <t>1664377</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1720608</t>
+          <t>1664377</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
